--- a/public/calculadora-inss-configuracoes.xlsx
+++ b/public/calculadora-inss-configuracoes.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7628A13-51E0-475D-A5EE-F939A655F314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50A6AAA3-2314-4165-86AB-1B2EA63D685C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculadora INSS 2026" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>CALCULADORA DE INSS 2026</t>
   </si>
@@ -187,6 +187,30 @@
       </rPr>
       <t xml:space="preserve"> - deixe este campo como está, pois são valores acimada faixa anterior</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Categoria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base_Calculo </t>
+  </si>
+  <si>
+    <t>Para Autônomos e MEI</t>
+  </si>
+  <si>
+    <t>Autônomo (Plano Normal)</t>
+  </si>
+  <si>
+    <t>Sobre Rendimento</t>
+  </si>
+  <si>
+    <t>Autônomo (Simplificado)</t>
+  </si>
+  <si>
+    <t>Sobre Salário Mínimo</t>
+  </si>
+  <si>
+    <t>MEI</t>
   </si>
 </sst>
 </file>
@@ -967,9 +991,62 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3966A465-3B87-486D-B430-97C74818EC22}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/calculadora-inss-configuracoes.xlsx
+++ b/public/calculadora-inss-configuracoes.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72207747-5123-4BA1-80E9-C636D7F5F337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F47169C2-1515-46F9-A0A7-C8836AFB4B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculadora INSS 2026" sheetId="1" r:id="rId1"/>
@@ -874,7 +874,7 @@
         <v>36</v>
       </c>
       <c r="B4">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
@@ -978,7 +978,7 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>1988.09</v>
+        <v>988.09</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>43</v>

--- a/public/calculadora-inss-configuracoes.xlsx
+++ b/public/calculadora-inss-configuracoes.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F47169C2-1515-46F9-A0A7-C8836AFB4B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72207747-5123-4BA1-80E9-C636D7F5F337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="3" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculadora INSS 2026" sheetId="1" r:id="rId1"/>
@@ -874,7 +874,7 @@
         <v>36</v>
       </c>
       <c r="B4">
-        <v>2026</v>
+        <v>2024</v>
       </c>
     </row>
   </sheetData>
@@ -978,7 +978,7 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <v>988.09</v>
+        <v>1988.09</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>43</v>
